--- a/frontend/src/assets/files/logindata.xlsx
+++ b/frontend/src/assets/files/logindata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\내문서\cau-fix-web\frontend\src\assests\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C34D4F9-E0F8-4E35-B010-B9CA73CB97B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC4BBFC-3FB5-40B8-BA24-3A1643D0017B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{E48136CC-7C3D-4819-A75A-073A29718EF6}"/>
   </bookViews>
@@ -25,13 +25,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pw</t>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>password</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>role</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>department</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기획팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김광명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이중앙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시설팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박병원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>외부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-1234-1234</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5678-5678</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-1111-2222</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -396,27 +460,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52665567-0E37-480E-82DD-DBCB454873B9}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>23012</v>
+        <v>1111</v>
       </c>
       <c r="B2">
-        <v>23012</v>
+        <v>1111</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2222</v>
+      </c>
+      <c r="B3">
+        <v>2222</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3333</v>
+      </c>
+      <c r="B4">
+        <v>3333</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/frontend/src/assets/files/logindata.xlsx
+++ b/frontend/src/assets/files/logindata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\내문서\cau-fix-web\frontend\src\assets\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC4BBFC-3FB5-40B8-BA24-3A1643D0017B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F66639-8FCF-4C3A-B9B0-405276A54AEB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{E48136CC-7C3D-4819-A75A-073A29718EF6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,10 +71,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>시설팀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>admin</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -87,15 +83,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>010-1234-1234</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-5678-5678</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-1111-2222</t>
+    <t>시설관리팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박점검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5678-1111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5678-2222</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5678-3333</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5678-4444</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -460,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52665567-0E37-480E-82DD-DBCB454873B9}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -499,8 +515,8 @@
       <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
-        <v>15</v>
+      <c r="F2">
+        <v>1234</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -517,10 +533,10 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -531,16 +547,76 @@
         <v>3333</v>
       </c>
       <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4444</v>
+      </c>
+      <c r="B5">
+        <v>4444</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5555</v>
+      </c>
+      <c r="B6">
+        <v>5555</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6666</v>
+      </c>
+      <c r="B7">
+        <v>6666</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
         <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/src/assets/files/logindata.xlsx
+++ b/frontend/src/assets/files/logindata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F66639-8FCF-4C3A-B9B0-405276A54AEB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4B23BC-748C-47A4-966B-C86E14B6FB53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{E48136CC-7C3D-4819-A75A-073A29718EF6}"/>
   </bookViews>
@@ -51,10 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기획팀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>user</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -112,6 +108,10 @@
   </si>
   <si>
     <t>010-5678-4444</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디지털전략팀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -507,13 +507,13 @@
         <v>1111</v>
       </c>
       <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>1234</v>
@@ -527,16 +527,16 @@
         <v>2222</v>
       </c>
       <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -547,13 +547,13 @@
         <v>3333</v>
       </c>
       <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4">
         <v>2222</v>
@@ -567,16 +567,16 @@
         <v>4444</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -587,16 +587,16 @@
         <v>5555</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -607,16 +607,16 @@
         <v>6666</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/src/assets/files/logindata.xlsx
+++ b/frontend/src/assets/files/logindata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4B23BC-748C-47A4-966B-C86E14B6FB53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1874A301-D251-467C-936E-5EADA6CE6323}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{E48136CC-7C3D-4819-A75A-073A29718EF6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -43,10 +43,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>department</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>phone</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -75,10 +71,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>외부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>시설관리팀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -112,6 +104,46 @@
   </si>
   <si>
     <t>디지털전략팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dept</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_approved</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>created_at</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>last_login_at</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-13 10:00AM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-14 10:00AM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계 / 소방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건축영선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비(의료, PC)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보안</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -476,10 +508,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52665567-0E37-480E-82DD-DBCB454873B9}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -493,13 +525,22 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1111</v>
       </c>
@@ -507,19 +548,28 @@
         <v>1111</v>
       </c>
       <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>1234</v>
       </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2222</v>
       </c>
@@ -527,19 +577,28 @@
         <v>2222</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3333</v>
       </c>
@@ -547,19 +606,28 @@
         <v>3333</v>
       </c>
       <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
       </c>
       <c r="F4">
         <v>2222</v>
       </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4444</v>
       </c>
@@ -567,19 +635,28 @@
         <v>4444</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5555</v>
       </c>
@@ -587,19 +664,28 @@
         <v>5555</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6666</v>
       </c>
@@ -607,16 +693,25 @@
         <v>6666</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/src/assets/files/logindata.xlsx
+++ b/frontend/src/assets/files/logindata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\frontend\src\assets\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\cau-fix\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1874A301-D251-467C-936E-5EADA6CE6323}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CDB6BA-F69B-4334-8133-95CB47F3D509}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{E48136CC-7C3D-4819-A75A-073A29718EF6}"/>
   </bookViews>
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,26 +43,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>user</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>김광명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>manager</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이중앙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>admin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>박병원</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -75,10 +59,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>박점검</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -91,10 +71,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>010-5678-2222</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>010-5678-3333</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -131,19 +107,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기계 / 소방</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>건축영선</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비(의료, PC)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>보안</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의료장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기/통신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김서울</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전산정보팀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>member_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -513,31 +509,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -548,13 +544,13 @@
         <v>1111</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>1234</v>
@@ -563,10 +559,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -577,25 +573,25 @@
         <v>2222</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -606,13 +602,13 @@
         <v>3333</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>2222</v>
@@ -621,10 +617,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -635,25 +631,25 @@
         <v>4444</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="F5" t="s">
-        <v>16</v>
+      <c r="F5">
+        <v>7777</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -664,25 +660,25 @@
         <v>5555</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -693,25 +689,25 @@
         <v>6666</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/src/assets/files/logindata.xlsx
+++ b/frontend/src/assets/files/logindata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\cau-fix\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CDB6BA-F69B-4334-8133-95CB47F3D509}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3C91B9-A897-4F4A-B806-9241657C3F21}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{E48136CC-7C3D-4819-A75A-073A29718EF6}"/>
   </bookViews>
@@ -25,122 +25,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
   <si>
     <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>password</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>role</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dept</t>
   </si>
   <si>
     <t>phone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_approved</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>last_login_at</t>
+  </si>
+  <si>
+    <t>is_deleted</t>
+  </si>
+  <si>
+    <t>deleted_at</t>
+  </si>
+  <si>
+    <t>user</t>
   </si>
   <si>
     <t>김광명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디지털전략팀</t>
+  </si>
+  <si>
+    <t>2026-04-13 10:00AM</t>
+  </si>
+  <si>
+    <t>2026-04-14 10:00AM</t>
+  </si>
+  <si>
+    <t>manager</t>
   </si>
   <si>
     <t>이중앙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계 / 소방</t>
+  </si>
+  <si>
+    <t>010-5678-1111</t>
+  </si>
+  <si>
+    <t>admin</t>
   </si>
   <si>
     <t>박병원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>시설관리팀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김시설</t>
+  </si>
+  <si>
+    <t>건축영선</t>
+  </si>
+  <si>
+    <t>010-5678-2222</t>
   </si>
   <si>
     <t>박점검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비(의료, PC)</t>
+  </si>
+  <si>
+    <t>010-5678-3333</t>
   </si>
   <si>
     <t>오관리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-5678-1111</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-5678-3333</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보안</t>
   </si>
   <si>
     <t>010-5678-4444</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>디지털전략팀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dept</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>is_approved</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>created_at</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>last_login_at</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-04-13 10:00AM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026-04-14 10:00AM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보안</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>의료장비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전기/통신</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김서울</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전산정보팀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>member_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-24 10:00AM</t>
   </si>
 </sst>
 </file>
@@ -504,12 +487,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52665567-0E37-480E-82DD-DBCB454873B9}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -518,25 +501,31 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1111</v>
       </c>
@@ -544,10 +533,10 @@
         <v>1111</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -559,13 +548,16 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2222</v>
       </c>
@@ -573,28 +565,31 @@
         <v>2222</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3333</v>
       </c>
@@ -602,13 +597,13 @@
         <v>3333</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>2222</v>
@@ -617,13 +612,16 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4444</v>
       </c>
@@ -631,28 +629,31 @@
         <v>4444</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <v>7777</v>
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5555</v>
       </c>
@@ -660,28 +661,31 @@
         <v>5555</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6666</v>
       </c>
@@ -689,25 +693,31 @@
         <v>6666</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/src/assets/files/logindata.xlsx
+++ b/frontend/src/assets/files/logindata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\cau-fix\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3C91B9-A897-4F4A-B806-9241657C3F21}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2F6FBD-A659-4101-ADB1-95F03430DB69}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{E48136CC-7C3D-4819-A75A-073A29718EF6}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>password</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>deleted_at</t>
   </si>
   <si>
-    <t>user</t>
-  </si>
-  <si>
     <t>김광명</t>
   </si>
   <si>
@@ -75,9 +69,6 @@
     <t>2026-04-14 10:00AM</t>
   </si>
   <si>
-    <t>manager</t>
-  </si>
-  <si>
     <t>이중앙</t>
   </si>
   <si>
@@ -87,9 +78,6 @@
     <t>010-5678-1111</t>
   </si>
   <si>
-    <t>admin</t>
-  </si>
-  <si>
     <t>박병원</t>
   </si>
   <si>
@@ -124,6 +112,22 @@
   </si>
   <si>
     <t>2026-04-24 10:00AM</t>
+  </si>
+  <si>
+    <t>member_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -492,37 +496,37 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -533,13 +537,13 @@
         <v>1111</v>
       </c>
       <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
       </c>
       <c r="F2">
         <v>1234</v>
@@ -548,10 +552,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -565,25 +569,25 @@
         <v>2222</v>
       </c>
       <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -597,13 +601,13 @@
         <v>3333</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>2222</v>
@@ -612,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -629,25 +633,25 @@
         <v>4444</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -661,25 +665,25 @@
         <v>5555</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -693,31 +697,31 @@
         <v>6666</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/src/assets/files/logindata.xlsx
+++ b/frontend/src/assets/files/logindata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\cau-fix\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2F6FBD-A659-4101-ADB1-95F03430DB69}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4856BBE8-DB8A-4C53-8FA6-F9ACDCCF4386}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{E48136CC-7C3D-4819-A75A-073A29718EF6}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>이중앙</t>
   </si>
   <si>
-    <t>기계 / 소방</t>
-  </si>
-  <si>
     <t>010-5678-1111</t>
   </si>
   <si>
@@ -87,16 +84,10 @@
     <t>김시설</t>
   </si>
   <si>
-    <t>건축영선</t>
-  </si>
-  <si>
     <t>010-5678-2222</t>
   </si>
   <si>
     <t>박점검</t>
-  </si>
-  <si>
-    <t>장비(의료, PC)</t>
   </si>
   <si>
     <t>010-5678-3333</t>
@@ -127,6 +118,18 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의료장비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건축/영선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계/소방</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -496,7 +499,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -537,7 +540,7 @@
         <v>1111</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -569,16 +572,16 @@
         <v>2222</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -601,13 +604,13 @@
         <v>3333</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
       </c>
       <c r="F4">
         <v>2222</v>
@@ -633,16 +636,16 @@
         <v>4444</v>
       </c>
       <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -665,16 +668,16 @@
         <v>5555</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -697,16 +700,16 @@
         <v>6666</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -721,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/src/assets/files/logindata.xlsx
+++ b/frontend/src/assets/files/logindata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\시설관리팀\내문서\cau-fix-web\cau-fix\frontend\src\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4856BBE8-DB8A-4C53-8FA6-F9ACDCCF4386}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1533AA46-FF89-4E30-AFF8-CE2EB621ADD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{E48136CC-7C3D-4819-A75A-073A29718EF6}"/>
   </bookViews>
@@ -129,7 +129,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기계/소방</t>
+    <t>전기/통신</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
